--- a/Projects/Ron Holland.xlsx
+++ b/Projects/Ron Holland.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632F4CFC-94CF-9144-A1E7-549A85822B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6943CD-5AAE-2F4B-BC72-3F49A1A4124C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6220" yWindow="680" windowWidth="24040" windowHeight="17680" firstSheet="2" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="6200" yWindow="660" windowWidth="24040" windowHeight="17580" firstSheet="2" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -3275,7 +3275,8 @@
     <col min="20" max="20" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.5" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="4.5" bestFit="1" customWidth="1"/>
@@ -4507,14 +4508,14 @@
   <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="15" bestFit="1" customWidth="1"/>
@@ -5080,31 +5081,31 @@
   <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
